--- a/per-stock/OKLO/financials.xlsx
+++ b/per-stock/OKLO/financials.xlsx
@@ -1,19 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Income stmt (annual)" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Income stmt (quarterly)" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balance sheet (annual)" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash flow (annual)" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash flow (quarterly)" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data flags" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="FY Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Income stmt (annual)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Income stmt (quarterly)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Balance sheet (annual)" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Balance sheet (quarterly)" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Cash flow (annual)" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Cash flow (quarterly)" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Data flags" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,7 +24,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="0.00&quot;x&quot;"/>
+    <numFmt numFmtId="166" formatCode="#,##0.0"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -61,11 +67,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -531,7 +540,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10830939136</v>
+        <v>10643028992</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -546,7 +555,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>8624950272</v>
+        <v>8437039616</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -578,7 +587,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-71.72899</v>
+        <v>-73.368195</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -717,11 +726,11 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-100000128</v>
+        <v>-153481000</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>yfinance info.freeCashflow</t>
+          <t>statement: TTM OCF - |capex| (yfinance quarterly_cashflow)</t>
         </is>
       </c>
     </row>
@@ -747,7 +756,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>62.25</v>
+        <v>61.17</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -791,6 +800,453 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="52" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Fiscal-year summary (GAAP, $ except where noted)</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>FY-3</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>FY-2</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>FY-1</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>TTM</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Source / formula</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Fiscal period end</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2023-12-31</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2024-12-31</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>TTM → 2026-03-31</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>annual statement headers; TTM = Σ last 4 quarters</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B3" s="3">
+        <f>'Income stmt (annual)'!D39</f>
+        <v/>
+      </c>
+      <c r="C3" s="3">
+        <f>'Income stmt (annual)'!C39</f>
+        <v/>
+      </c>
+      <c r="D3" s="3">
+        <f>'Income stmt (annual)'!B39</f>
+        <v/>
+      </c>
+      <c r="E3" s="3">
+        <f>SUM('Income stmt (quarterly)'!B39:E39)</f>
+        <v/>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Total Revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Gross profit</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr"/>
+      <c r="C4" s="3" t="inlineStr"/>
+      <c r="D4" s="3" t="inlineStr"/>
+      <c r="E4" s="3" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Gross Profit (GAAP)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Gross margin %</t>
+        </is>
+      </c>
+      <c r="B5" s="4">
+        <f>IFERROR(B4/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C5" s="4">
+        <f>IFERROR(C4/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D5" s="4">
+        <f>IFERROR(D4/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E5" s="4">
+        <f>IFERROR(E4/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>GAAP = gross profit / revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Operating income</t>
+        </is>
+      </c>
+      <c r="B6" s="3">
+        <f>'Income stmt (annual)'!D32</f>
+        <v/>
+      </c>
+      <c r="C6" s="3">
+        <f>'Income stmt (annual)'!C32</f>
+        <v/>
+      </c>
+      <c r="D6" s="3">
+        <f>'Income stmt (annual)'!B32</f>
+        <v/>
+      </c>
+      <c r="E6" s="3">
+        <f>SUM('Income stmt (quarterly)'!B32:E32)</f>
+        <v/>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Operating Income</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Operating margin %</t>
+        </is>
+      </c>
+      <c r="B7" s="4">
+        <f>IFERROR(B6/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C7" s="4">
+        <f>IFERROR(C6/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D7" s="4">
+        <f>IFERROR(D6/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E7" s="4">
+        <f>IFERROR(E6/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F7">
+        <f> operating income / revenue</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="B8" s="3">
+        <f>'Income stmt (annual)'!D9</f>
+        <v/>
+      </c>
+      <c r="C8" s="3">
+        <f>'Income stmt (annual)'!C9</f>
+        <v/>
+      </c>
+      <c r="D8" s="3">
+        <f>'Income stmt (annual)'!B9</f>
+        <v/>
+      </c>
+      <c r="E8" s="3">
+        <f>SUM('Income stmt (quarterly)'!B9:E9)</f>
+        <v/>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Free cash flow</t>
+        </is>
+      </c>
+      <c r="B9" s="3">
+        <f>'Cash flow (annual)'!D2</f>
+        <v/>
+      </c>
+      <c r="C9" s="3">
+        <f>'Cash flow (annual)'!C2</f>
+        <v/>
+      </c>
+      <c r="D9" s="3">
+        <f>'Cash flow (annual)'!B2</f>
+        <v/>
+      </c>
+      <c r="E9" s="3">
+        <f>SUM('Cash flow (quarterly)'!B2:E2)</f>
+        <v/>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>FCF = OCF − capex</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>FCF margin %</t>
+        </is>
+      </c>
+      <c r="B10" s="4">
+        <f>IFERROR(B9/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C10" s="4">
+        <f>IFERROR(C9/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D10" s="4">
+        <f>IFERROR(D9/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E10" s="4">
+        <f>IFERROR(E9/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F10">
+        <f> FCF / revenue</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Capex</t>
+        </is>
+      </c>
+      <c r="B11" s="3">
+        <f>-'Cash flow (annual)'!D4</f>
+        <v/>
+      </c>
+      <c r="C11" s="3">
+        <f>-'Cash flow (annual)'!C4</f>
+        <v/>
+      </c>
+      <c r="D11" s="3">
+        <f>-'Cash flow (annual)'!B4</f>
+        <v/>
+      </c>
+      <c r="E11" s="3">
+        <f>-SUM('Cash flow (quarterly)'!B4:E4)</f>
+        <v/>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Capex (shown positive)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Capex / revenue %</t>
+        </is>
+      </c>
+      <c r="B12" s="4">
+        <f>IFERROR(B11/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C12" s="4">
+        <f>IFERROR(C11/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D12" s="4">
+        <f>IFERROR(D11/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E12" s="4">
+        <f>IFERROR(E11/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F12">
+        <f> capex / revenue</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Net debt</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr"/>
+      <c r="C13" s="3" t="inlineStr"/>
+      <c r="D13" s="3" t="inlineStr"/>
+      <c r="E13" s="3" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Net debt; TTM = MRQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Net debt / EBITDA</t>
+        </is>
+      </c>
+      <c r="B14" s="5">
+        <f>IFERROR(B13/B8,"")</f>
+        <v/>
+      </c>
+      <c r="C14" s="5">
+        <f>IFERROR(C13/C8,"")</f>
+        <v/>
+      </c>
+      <c r="D14" s="5">
+        <f>IFERROR(D13/D8,"")</f>
+        <v/>
+      </c>
+      <c r="E14" s="5">
+        <f>IFERROR(E13/E8,"")</f>
+        <v/>
+      </c>
+      <c r="F14">
+        <f> net debt / EBITDA</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Share count (period-end, M)</t>
+        </is>
+      </c>
+      <c r="B15" s="6">
+        <f>'Balance sheet (annual)'!D2/1e6</f>
+        <v/>
+      </c>
+      <c r="C15" s="6">
+        <f>'Balance sheet (annual)'!C2/1e6</f>
+        <v/>
+      </c>
+      <c r="D15" s="6">
+        <f>'Balance sheet (annual)'!B2/1e6</f>
+        <v/>
+      </c>
+      <c r="E15" s="6">
+        <f>'Balance sheet (quarterly)'!B2/1e6</f>
+        <v/>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>shares ÷ 1e6; TTM = MRQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Share count YoY %</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr"/>
+      <c r="C16" s="4">
+        <f>IFERROR(C15/B15-1,"")</f>
+        <v/>
+      </c>
+      <c r="D16" s="4">
+        <f>IFERROR(D15/C15-1,"")</f>
+        <v/>
+      </c>
+      <c r="E16" s="4">
+        <f>IFERROR(E15/D15-1,"")</f>
+        <v/>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>vs prior period</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1137,7 +1593,9 @@
           <t>Diluted Average Shares</t>
         </is>
       </c>
-      <c r="B17" s="3" t="n"/>
+      <c r="B17" s="3" t="n">
+        <v>146351775</v>
+      </c>
       <c r="C17" s="3" t="n">
         <v>98910013</v>
       </c>
@@ -1147,9 +1605,7 @@
       <c r="E17" s="3" t="n">
         <v>70320242</v>
       </c>
-      <c r="F17" s="3" t="n">
-        <v>70320242</v>
-      </c>
+      <c r="F17" s="3" t="n"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1157,7 +1613,9 @@
           <t>Basic Average Shares</t>
         </is>
       </c>
-      <c r="B18" s="3" t="n"/>
+      <c r="B18" s="3" t="n">
+        <v>146351775</v>
+      </c>
       <c r="C18" s="3" t="n">
         <v>98910013</v>
       </c>
@@ -1167,9 +1625,7 @@
       <c r="E18" s="3" t="n">
         <v>70320242</v>
       </c>
-      <c r="F18" s="3" t="n">
-        <v>70320242</v>
-      </c>
+      <c r="F18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1177,7 +1633,9 @@
           <t>Diluted EPS</t>
         </is>
       </c>
-      <c r="B19" s="3" t="n"/>
+      <c r="B19" s="3" t="n">
+        <v>-0.72</v>
+      </c>
       <c r="C19" s="3" t="n">
         <v>-0.74</v>
       </c>
@@ -1187,9 +1645,7 @@
       <c r="E19" s="3" t="n">
         <v>-0.142546</v>
       </c>
-      <c r="F19" s="3" t="n">
-        <v>-0.07332900000000001</v>
-      </c>
+      <c r="F19" s="3" t="n"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1197,7 +1653,9 @@
           <t>Basic EPS</t>
         </is>
       </c>
-      <c r="B20" s="3" t="n"/>
+      <c r="B20" s="3" t="n">
+        <v>-0.72</v>
+      </c>
       <c r="C20" s="3" t="n">
         <v>-0.74</v>
       </c>
@@ -1207,9 +1665,7 @@
       <c r="E20" s="3" t="n">
         <v>-0.142546</v>
       </c>
-      <c r="F20" s="3" t="n">
-        <v>-0.07332900000000001</v>
-      </c>
+      <c r="F20" s="3" t="n"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1604,13 +2060,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G40"/>
+  <dimension ref="A1:H40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1620,6 +2076,7 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1630,30 +2087,35 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>2025-12-31</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>2025-06-30</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>2025-03-31</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>2024-12-31</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>2024-09-30</t>
         </is>
@@ -1678,9 +2140,10 @@
         <v>0</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>431751.39</v>
+        <v>0</v>
       </c>
       <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1689,21 +2152,22 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>0.025396</v>
-      </c>
-      <c r="C3" s="3" t="n">
-        <v>0.21</v>
       </c>
       <c r="D3" s="3" t="n">
         <v>0.21</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>0.303</v>
+        <v>0.21</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.21</v>
+        <v>0.310175</v>
       </c>
       <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1712,21 +2176,22 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
+        <v>-51086000</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>-56947000</v>
       </c>
-      <c r="C4" s="3" t="n">
+      <c r="D4" s="3" t="n">
         <v>-36185000</v>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="E4" s="3" t="n">
         <v>-27890000</v>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="F4" s="3" t="n">
         <v>-17750000</v>
       </c>
-      <c r="F4" s="3" t="n">
-        <v>-17346926</v>
-      </c>
       <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1738,10 +2203,11 @@
       <c r="C5" s="3" t="n"/>
       <c r="D5" s="3" t="n"/>
       <c r="E5" s="3" t="n"/>
-      <c r="F5" s="3" t="n">
+      <c r="F5" s="3" t="n"/>
+      <c r="G5" s="3" t="n">
         <v>2055959</v>
       </c>
-      <c r="G5" s="3" t="n"/>
+      <c r="H5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1753,10 +2219,11 @@
       <c r="C6" s="3" t="n"/>
       <c r="D6" s="3" t="n"/>
       <c r="E6" s="3" t="n"/>
-      <c r="F6" s="3" t="n">
+      <c r="F6" s="3" t="n"/>
+      <c r="G6" s="3" t="n">
         <v>2055959</v>
       </c>
-      <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1765,21 +2232,22 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
+        <v>-33065000</v>
+      </c>
+      <c r="C7" s="3" t="n">
         <v>-41446000</v>
       </c>
-      <c r="C7" s="3" t="n">
+      <c r="D7" s="3" t="n">
         <v>-29722000</v>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="E7" s="3" t="n">
         <v>-24685000</v>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="F7" s="3" t="n">
         <v>-9810000</v>
       </c>
-      <c r="F7" s="3" t="n">
-        <v>-10288767</v>
-      </c>
       <c r="G7" s="3" t="n"/>
+      <c r="H7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1788,21 +2256,22 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
+        <v>163000</v>
+      </c>
+      <c r="C8" s="3" t="n">
         <v>149000</v>
       </c>
-      <c r="C8" s="3" t="n">
+      <c r="D8" s="3" t="n">
         <v>124000</v>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="E8" s="3" t="n">
         <v>125000</v>
       </c>
-      <c r="E8" s="3" t="n">
+      <c r="F8" s="3" t="n">
         <v>124000</v>
       </c>
-      <c r="F8" s="3" t="n">
-        <v>87580</v>
-      </c>
       <c r="G8" s="3" t="n"/>
+      <c r="H8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1811,21 +2280,22 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
+        <v>-51086000</v>
+      </c>
+      <c r="C9" s="3" t="n">
         <v>-56947000</v>
       </c>
-      <c r="C9" s="3" t="n">
+      <c r="D9" s="3" t="n">
         <v>-36185000</v>
       </c>
-      <c r="D9" s="3" t="n">
+      <c r="E9" s="3" t="n">
         <v>-27890000</v>
       </c>
-      <c r="E9" s="3" t="n">
+      <c r="F9" s="3" t="n">
         <v>-17750000</v>
       </c>
-      <c r="F9" s="3" t="n">
-        <v>-15290967</v>
-      </c>
       <c r="G9" s="3" t="n"/>
+      <c r="H9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1834,21 +2304,22 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
+        <v>-51249000</v>
+      </c>
+      <c r="C10" s="3" t="n">
         <v>-57096000</v>
       </c>
-      <c r="C10" s="3" t="n">
+      <c r="D10" s="3" t="n">
         <v>-36309000</v>
       </c>
-      <c r="D10" s="3" t="n">
+      <c r="E10" s="3" t="n">
         <v>-28015000</v>
       </c>
-      <c r="E10" s="3" t="n">
+      <c r="F10" s="3" t="n">
         <v>-17874000</v>
       </c>
-      <c r="F10" s="3" t="n">
-        <v>-15378547</v>
-      </c>
       <c r="G10" s="3" t="n"/>
+      <c r="H10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1857,21 +2328,22 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
+        <v>21339000</v>
+      </c>
+      <c r="C11" s="3" t="n">
         <v>14570000</v>
       </c>
-      <c r="C11" s="3" t="n">
+      <c r="D11" s="3" t="n">
         <v>7118000</v>
       </c>
-      <c r="D11" s="3" t="n">
+      <c r="E11" s="3" t="n">
         <v>3761000</v>
       </c>
-      <c r="E11" s="3" t="n">
+      <c r="F11" s="3" t="n">
         <v>3653000</v>
       </c>
-      <c r="F11" s="3" t="n">
-        <v>3328237</v>
-      </c>
       <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1880,21 +2352,22 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
+        <v>21339000</v>
+      </c>
+      <c r="C12" s="3" t="n">
         <v>14570000</v>
       </c>
-      <c r="C12" s="3" t="n">
+      <c r="D12" s="3" t="n">
         <v>7118000</v>
       </c>
-      <c r="D12" s="3" t="n">
+      <c r="E12" s="3" t="n">
         <v>3761000</v>
       </c>
-      <c r="E12" s="3" t="n">
+      <c r="F12" s="3" t="n">
         <v>3653000</v>
       </c>
-      <c r="F12" s="3" t="n">
-        <v>3328237</v>
-      </c>
       <c r="G12" s="3" t="n"/>
+      <c r="H12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1903,21 +2376,22 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
+        <v>-33065000</v>
+      </c>
+      <c r="C13" s="3" t="n">
         <v>-41446000</v>
       </c>
-      <c r="C13" s="3" t="n">
+      <c r="D13" s="3" t="n">
         <v>-29722000</v>
       </c>
-      <c r="D13" s="3" t="n">
+      <c r="E13" s="3" t="n">
         <v>-24685000</v>
       </c>
-      <c r="E13" s="3" t="n">
+      <c r="F13" s="3" t="n">
         <v>-9810000</v>
       </c>
-      <c r="F13" s="3" t="n">
-        <v>-11912974.61</v>
-      </c>
       <c r="G13" s="3" t="n"/>
+      <c r="H13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1926,21 +2400,22 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
+        <v>-33065000</v>
+      </c>
+      <c r="C14" s="3" t="n">
         <v>-41446000</v>
       </c>
-      <c r="C14" s="3" t="n">
+      <c r="D14" s="3" t="n">
         <v>-29722000</v>
       </c>
-      <c r="D14" s="3" t="n">
+      <c r="E14" s="3" t="n">
         <v>-24685000</v>
       </c>
-      <c r="E14" s="3" t="n">
+      <c r="F14" s="3" t="n">
         <v>-9810000</v>
       </c>
-      <c r="F14" s="3" t="n">
-        <v>-10288767</v>
-      </c>
       <c r="G14" s="3" t="n"/>
+      <c r="H14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1949,21 +2424,22 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
+        <v>51249000</v>
+      </c>
+      <c r="C15" s="3" t="n">
         <v>57096000</v>
       </c>
-      <c r="C15" s="3" t="n">
+      <c r="D15" s="3" t="n">
         <v>36309000</v>
       </c>
-      <c r="D15" s="3" t="n">
+      <c r="E15" s="3" t="n">
         <v>28015000</v>
       </c>
-      <c r="E15" s="3" t="n">
+      <c r="F15" s="3" t="n">
         <v>17874000</v>
       </c>
-      <c r="F15" s="3" t="n">
-        <v>15378547</v>
-      </c>
       <c r="G15" s="3" t="n"/>
+      <c r="H15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1972,21 +2448,22 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
+        <v>-51249000</v>
+      </c>
+      <c r="C16" s="3" t="n">
         <v>-57096000</v>
       </c>
-      <c r="C16" s="3" t="n">
+      <c r="D16" s="3" t="n">
         <v>-36309000</v>
       </c>
-      <c r="D16" s="3" t="n">
+      <c r="E16" s="3" t="n">
         <v>-28015000</v>
       </c>
-      <c r="E16" s="3" t="n">
+      <c r="F16" s="3" t="n">
         <v>-17874000</v>
       </c>
-      <c r="F16" s="3" t="n">
-        <v>-15378547</v>
-      </c>
       <c r="G16" s="3" t="n"/>
+      <c r="H16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1994,18 +2471,21 @@
           <t>Diluted Average Shares</t>
         </is>
       </c>
-      <c r="B17" s="3" t="n"/>
-      <c r="C17" s="3" t="n">
+      <c r="B17" s="3" t="n">
+        <v>170333746</v>
+      </c>
+      <c r="C17" s="3" t="n"/>
+      <c r="D17" s="3" t="n">
         <v>150364909</v>
       </c>
-      <c r="D17" s="3" t="n">
+      <c r="E17" s="3" t="n">
         <v>140085498</v>
       </c>
-      <c r="E17" s="3" t="n">
+      <c r="F17" s="3" t="n">
         <v>138109974</v>
       </c>
-      <c r="F17" s="3" t="n"/>
-      <c r="G17" s="3" t="n">
+      <c r="G17" s="3" t="n"/>
+      <c r="H17" s="3" t="n">
         <v>122134375</v>
       </c>
     </row>
@@ -2015,18 +2495,21 @@
           <t>Basic Average Shares</t>
         </is>
       </c>
-      <c r="B18" s="3" t="n"/>
-      <c r="C18" s="3" t="n">
+      <c r="B18" s="3" t="n">
+        <v>170333746</v>
+      </c>
+      <c r="C18" s="3" t="n"/>
+      <c r="D18" s="3" t="n">
         <v>150364909</v>
       </c>
-      <c r="D18" s="3" t="n">
+      <c r="E18" s="3" t="n">
         <v>140085498</v>
       </c>
-      <c r="E18" s="3" t="n">
+      <c r="F18" s="3" t="n">
         <v>138109974</v>
       </c>
-      <c r="F18" s="3" t="n"/>
-      <c r="G18" s="3" t="n">
+      <c r="G18" s="3" t="n"/>
+      <c r="H18" s="3" t="n">
         <v>122134375</v>
       </c>
     </row>
@@ -2036,18 +2519,21 @@
           <t>Diluted EPS</t>
         </is>
       </c>
-      <c r="B19" s="3" t="n"/>
-      <c r="C19" s="3" t="n">
+      <c r="B19" s="3" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="C19" s="3" t="n"/>
+      <c r="D19" s="3" t="n">
         <v>-0.2</v>
       </c>
-      <c r="D19" s="3" t="n">
+      <c r="E19" s="3" t="n">
         <v>-0.18</v>
       </c>
-      <c r="E19" s="3" t="n">
+      <c r="F19" s="3" t="n">
         <v>-0.07000000000000001</v>
       </c>
-      <c r="F19" s="3" t="n"/>
-      <c r="G19" s="3" t="n">
+      <c r="G19" s="3" t="n"/>
+      <c r="H19" s="3" t="n">
         <v>-0.08</v>
       </c>
     </row>
@@ -2057,18 +2543,21 @@
           <t>Basic EPS</t>
         </is>
       </c>
-      <c r="B20" s="3" t="n"/>
-      <c r="C20" s="3" t="n">
+      <c r="B20" s="3" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="C20" s="3" t="n"/>
+      <c r="D20" s="3" t="n">
         <v>-0.2</v>
       </c>
-      <c r="D20" s="3" t="n">
+      <c r="E20" s="3" t="n">
         <v>-0.18</v>
       </c>
-      <c r="E20" s="3" t="n">
+      <c r="F20" s="3" t="n">
         <v>-0.07000000000000001</v>
       </c>
-      <c r="F20" s="3" t="n"/>
-      <c r="G20" s="3" t="n">
+      <c r="G20" s="3" t="n"/>
+      <c r="H20" s="3" t="n">
         <v>-0.08</v>
       </c>
     </row>
@@ -2079,21 +2568,22 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
+        <v>-33065000</v>
+      </c>
+      <c r="C21" s="3" t="n">
         <v>-41446000</v>
       </c>
-      <c r="C21" s="3" t="n">
+      <c r="D21" s="3" t="n">
         <v>-29722000</v>
       </c>
-      <c r="D21" s="3" t="n">
+      <c r="E21" s="3" t="n">
         <v>-24685000</v>
       </c>
-      <c r="E21" s="3" t="n">
+      <c r="F21" s="3" t="n">
         <v>-9810000</v>
       </c>
-      <c r="F21" s="3" t="n">
-        <v>477645833</v>
-      </c>
       <c r="G21" s="3" t="n"/>
+      <c r="H21" s="3" t="n"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2102,21 +2592,22 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
+        <v>-33065000</v>
+      </c>
+      <c r="C22" s="3" t="n">
         <v>-41446000</v>
       </c>
-      <c r="C22" s="3" t="n">
+      <c r="D22" s="3" t="n">
         <v>-29722000</v>
       </c>
-      <c r="D22" s="3" t="n">
+      <c r="E22" s="3" t="n">
         <v>-24685000</v>
       </c>
-      <c r="E22" s="3" t="n">
+      <c r="F22" s="3" t="n">
         <v>-9810000</v>
       </c>
-      <c r="F22" s="3" t="n">
-        <v>477645833</v>
-      </c>
       <c r="G22" s="3" t="n"/>
+      <c r="H22" s="3" t="n"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2125,21 +2616,22 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
+        <v>-33065000</v>
+      </c>
+      <c r="C23" s="3" t="n">
         <v>-41446000</v>
       </c>
-      <c r="C23" s="3" t="n">
+      <c r="D23" s="3" t="n">
         <v>-29722000</v>
       </c>
-      <c r="D23" s="3" t="n">
+      <c r="E23" s="3" t="n">
         <v>-24685000</v>
       </c>
-      <c r="E23" s="3" t="n">
+      <c r="F23" s="3" t="n">
         <v>-9810000</v>
       </c>
-      <c r="F23" s="3" t="n">
-        <v>-10288767</v>
-      </c>
       <c r="G23" s="3" t="n"/>
+      <c r="H23" s="3" t="n"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2148,21 +2640,22 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
+        <v>-33065000</v>
+      </c>
+      <c r="C24" s="3" t="n">
         <v>-41446000</v>
       </c>
-      <c r="C24" s="3" t="n">
+      <c r="D24" s="3" t="n">
         <v>-29722000</v>
       </c>
-      <c r="D24" s="3" t="n">
+      <c r="E24" s="3" t="n">
         <v>-24685000</v>
       </c>
-      <c r="E24" s="3" t="n">
+      <c r="F24" s="3" t="n">
         <v>-9810000</v>
       </c>
-      <c r="F24" s="3" t="n">
-        <v>-10288767</v>
-      </c>
       <c r="G24" s="3" t="n"/>
+      <c r="H24" s="3" t="n"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2171,21 +2664,22 @@
         </is>
       </c>
       <c r="B25" s="3" t="n">
+        <v>-33065000</v>
+      </c>
+      <c r="C25" s="3" t="n">
         <v>-41446000</v>
       </c>
-      <c r="C25" s="3" t="n">
+      <c r="D25" s="3" t="n">
         <v>-29722000</v>
       </c>
-      <c r="D25" s="3" t="n">
+      <c r="E25" s="3" t="n">
         <v>-24685000</v>
       </c>
-      <c r="E25" s="3" t="n">
+      <c r="F25" s="3" t="n">
         <v>-9810000</v>
       </c>
-      <c r="F25" s="3" t="n">
-        <v>-10288767</v>
-      </c>
       <c r="G25" s="3" t="n"/>
+      <c r="H25" s="3" t="n"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2194,21 +2688,22 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
+        <v>3155000</v>
+      </c>
+      <c r="C26" s="3" t="n">
         <v>-1080000</v>
       </c>
-      <c r="C26" s="3" t="n">
+      <c r="D26" s="3" t="n">
         <v>531000</v>
       </c>
-      <c r="D26" s="3" t="n">
+      <c r="E26" s="3" t="n">
         <v>431000</v>
       </c>
-      <c r="E26" s="3" t="n">
+      <c r="F26" s="3" t="n">
         <v>-4411000</v>
       </c>
-      <c r="F26" s="3" t="n">
-        <v>294416</v>
-      </c>
       <c r="G26" s="3" t="n"/>
+      <c r="H26" s="3" t="n"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2217,21 +2712,22 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
+        <v>-29910000</v>
+      </c>
+      <c r="C27" s="3" t="n">
         <v>-42526000</v>
       </c>
-      <c r="C27" s="3" t="n">
+      <c r="D27" s="3" t="n">
         <v>-29191000</v>
       </c>
-      <c r="D27" s="3" t="n">
+      <c r="E27" s="3" t="n">
         <v>-24254000</v>
       </c>
-      <c r="E27" s="3" t="n">
+      <c r="F27" s="3" t="n">
         <v>-14221000</v>
       </c>
-      <c r="F27" s="3" t="n">
-        <v>-9994351</v>
-      </c>
       <c r="G27" s="3" t="n"/>
+      <c r="H27" s="3" t="n"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2243,10 +2739,11 @@
       <c r="C28" s="3" t="n"/>
       <c r="D28" s="3" t="n"/>
       <c r="E28" s="3" t="n"/>
-      <c r="F28" s="3" t="n">
+      <c r="F28" s="3" t="n"/>
+      <c r="G28" s="3" t="n">
         <v>2055959</v>
       </c>
-      <c r="G28" s="3" t="n"/>
+      <c r="H28" s="3" t="n"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2258,10 +2755,11 @@
       <c r="C29" s="3" t="n"/>
       <c r="D29" s="3" t="n"/>
       <c r="E29" s="3" t="n"/>
-      <c r="F29" s="3" t="n">
+      <c r="F29" s="3" t="n"/>
+      <c r="G29" s="3" t="n">
         <v>2055959</v>
       </c>
-      <c r="G29" s="3" t="n"/>
+      <c r="H29" s="3" t="n"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2270,21 +2768,22 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
+        <v>21339000</v>
+      </c>
+      <c r="C30" s="3" t="n">
         <v>14570000</v>
       </c>
-      <c r="C30" s="3" t="n">
+      <c r="D30" s="3" t="n">
         <v>7118000</v>
       </c>
-      <c r="D30" s="3" t="n">
+      <c r="E30" s="3" t="n">
         <v>3761000</v>
       </c>
-      <c r="E30" s="3" t="n">
+      <c r="F30" s="3" t="n">
         <v>3653000</v>
       </c>
-      <c r="F30" s="3" t="n">
-        <v>3328237</v>
-      </c>
       <c r="G30" s="3" t="n"/>
+      <c r="H30" s="3" t="n"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2293,21 +2792,22 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
+        <v>21339000</v>
+      </c>
+      <c r="C31" s="3" t="n">
         <v>14570000</v>
       </c>
-      <c r="C31" s="3" t="n">
+      <c r="D31" s="3" t="n">
         <v>7118000</v>
       </c>
-      <c r="D31" s="3" t="n">
+      <c r="E31" s="3" t="n">
         <v>3761000</v>
       </c>
-      <c r="E31" s="3" t="n">
+      <c r="F31" s="3" t="n">
         <v>3653000</v>
       </c>
-      <c r="F31" s="3" t="n">
-        <v>3328237</v>
-      </c>
       <c r="G31" s="3" t="n"/>
+      <c r="H31" s="3" t="n"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2316,21 +2816,22 @@
         </is>
       </c>
       <c r="B32" s="3" t="n">
+        <v>-51249000</v>
+      </c>
+      <c r="C32" s="3" t="n">
         <v>-57096000</v>
       </c>
-      <c r="C32" s="3" t="n">
+      <c r="D32" s="3" t="n">
         <v>-36309000</v>
       </c>
-      <c r="D32" s="3" t="n">
+      <c r="E32" s="3" t="n">
         <v>-28015000</v>
       </c>
-      <c r="E32" s="3" t="n">
+      <c r="F32" s="3" t="n">
         <v>-17874000</v>
       </c>
-      <c r="F32" s="3" t="n">
-        <v>-15378547</v>
-      </c>
       <c r="G32" s="3" t="n"/>
+      <c r="H32" s="3" t="n"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2339,21 +2840,22 @@
         </is>
       </c>
       <c r="B33" s="3" t="n">
+        <v>51249000</v>
+      </c>
+      <c r="C33" s="3" t="n">
         <v>57096000</v>
       </c>
-      <c r="C33" s="3" t="n">
+      <c r="D33" s="3" t="n">
         <v>36309000</v>
       </c>
-      <c r="D33" s="3" t="n">
+      <c r="E33" s="3" t="n">
         <v>28015000</v>
       </c>
-      <c r="E33" s="3" t="n">
+      <c r="F33" s="3" t="n">
         <v>17874000</v>
       </c>
-      <c r="F33" s="3" t="n">
-        <v>15378547</v>
-      </c>
       <c r="G33" s="3" t="n"/>
+      <c r="H33" s="3" t="n"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2362,21 +2864,22 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
+        <v>27049000</v>
+      </c>
+      <c r="C34" s="3" t="n">
         <v>24593000</v>
       </c>
-      <c r="C34" s="3" t="n">
+      <c r="D34" s="3" t="n">
         <v>14945000</v>
       </c>
-      <c r="D34" s="3" t="n">
+      <c r="E34" s="3" t="n">
         <v>11468000</v>
       </c>
-      <c r="E34" s="3" t="n">
+      <c r="F34" s="3" t="n">
         <v>7846000</v>
       </c>
-      <c r="F34" s="3" t="n">
-        <v>7282146</v>
-      </c>
       <c r="G34" s="3" t="n"/>
+      <c r="H34" s="3" t="n"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2385,21 +2888,22 @@
         </is>
       </c>
       <c r="B35" s="3" t="n">
+        <v>24200000</v>
+      </c>
+      <c r="C35" s="3" t="n">
         <v>32503000</v>
       </c>
-      <c r="C35" s="3" t="n">
+      <c r="D35" s="3" t="n">
         <v>21364000</v>
       </c>
-      <c r="D35" s="3" t="n">
+      <c r="E35" s="3" t="n">
         <v>16547000</v>
       </c>
-      <c r="E35" s="3" t="n">
+      <c r="F35" s="3" t="n">
         <v>10028000</v>
       </c>
-      <c r="F35" s="3" t="n">
-        <v>8096401</v>
-      </c>
       <c r="G35" s="3" t="n"/>
+      <c r="H35" s="3" t="n"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2408,21 +2912,22 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
+        <v>24200000</v>
+      </c>
+      <c r="C36" s="3" t="n">
         <v>32503000</v>
       </c>
-      <c r="C36" s="3" t="n">
+      <c r="D36" s="3" t="n">
         <v>21364000</v>
       </c>
-      <c r="D36" s="3" t="n">
+      <c r="E36" s="3" t="n">
         <v>16547000</v>
       </c>
-      <c r="E36" s="3" t="n">
+      <c r="F36" s="3" t="n">
         <v>10028000</v>
       </c>
-      <c r="F36" s="3" t="n">
-        <v>8096401</v>
-      </c>
       <c r="G36" s="3" t="n"/>
+      <c r="H36" s="3" t="n"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2431,21 +2936,22 @@
         </is>
       </c>
       <c r="B37" s="3" t="n">
+        <v>24200000</v>
+      </c>
+      <c r="C37" s="3" t="n">
         <v>32503000</v>
       </c>
-      <c r="C37" s="3" t="n">
+      <c r="D37" s="3" t="n">
         <v>21364000</v>
       </c>
-      <c r="D37" s="3" t="n">
+      <c r="E37" s="3" t="n">
         <v>16547000</v>
       </c>
-      <c r="E37" s="3" t="n">
+      <c r="F37" s="3" t="n">
         <v>10028000</v>
       </c>
-      <c r="F37" s="3" t="n">
-        <v>16407206</v>
-      </c>
       <c r="G37" s="3" t="n"/>
+      <c r="H37" s="3" t="n"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2458,7 +2964,8 @@
       <c r="D38" s="3" t="n"/>
       <c r="E38" s="3" t="n"/>
       <c r="F38" s="3" t="n"/>
-      <c r="G38" s="3" t="n">
+      <c r="G38" s="3" t="n"/>
+      <c r="H38" s="3" t="n">
         <v>3168622</v>
       </c>
     </row>
@@ -2484,6 +2991,7 @@
         <v>0</v>
       </c>
       <c r="G39" s="3" t="n"/>
+      <c r="H39" s="3" t="n"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2507,13 +3015,14 @@
         <v>0</v>
       </c>
       <c r="G40" s="3" t="n"/>
+      <c r="H40" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3817,7 +4326,1641 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H68"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>2024-12-31</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Ordinary Shares Number</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>173867839</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>160514103</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>156186456</v>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>147595514</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>139188804</v>
+      </c>
+      <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Share Issued</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>173867839</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>160514103</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>156186456</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>147595514</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>139188804</v>
+      </c>
+      <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Total Debt</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>2620000</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>1450000</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>1944000</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>2139000</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>2053000</v>
+      </c>
+      <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Tangible Book Value</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>2604508000</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>1442089000</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>1171366000</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>662191000</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>235110000</v>
+      </c>
+      <c r="G5" s="3" t="n"/>
+      <c r="H5" s="3" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Invested Capital</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>2638629000</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>1476210000</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>1205869000</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>696686000</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>269590000</v>
+      </c>
+      <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Working Capital</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>2188522000</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>1228223000</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>917976000</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>535048000</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>199251000</v>
+      </c>
+      <c r="G7" s="3" t="n"/>
+      <c r="H7" s="3" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Net Tangible Assets</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>2604508000</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>1442089000</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>1171366000</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>662191000</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>235110000</v>
+      </c>
+      <c r="G8" s="3" t="n"/>
+      <c r="H8" s="3" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Capital Lease Obligations</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>2620000</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>1450000</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>1661000</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>1864000</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>1793000</v>
+      </c>
+      <c r="G9" s="3" t="n"/>
+      <c r="H9" s="3" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Common Stock Equity</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>2638629000</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>1476210000</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>1205586000</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>696411000</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>269330000</v>
+      </c>
+      <c r="G10" s="3" t="n"/>
+      <c r="H10" s="3" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Total Capitalization</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>2638629000</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>1476210000</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>1205586000</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>696411000</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>269330000</v>
+      </c>
+      <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Total Equity Gross Minority Interest</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>2638629000</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>1476210000</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>1205586000</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>696411000</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>269330000</v>
+      </c>
+      <c r="G12" s="3" t="n"/>
+      <c r="H12" s="3" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Stockholders Equity</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>2638629000</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>1476210000</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>1205586000</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>696411000</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>269330000</v>
+      </c>
+      <c r="G13" s="3" t="n"/>
+      <c r="H13" s="3" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Gains Losses Not Affecting Retained Earnings</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>-1482000</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>1179000</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>3576000</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>1323000</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>1652000</v>
+      </c>
+      <c r="G14" s="3" t="n"/>
+      <c r="H14" s="3" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Other Equity Adjustments</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>-1482000</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>1179000</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>3576000</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>1323000</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>1652000</v>
+      </c>
+      <c r="G15" s="3" t="n"/>
+      <c r="H15" s="3" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Retained Earnings</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>-273837000</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>-240772000</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>-199326000</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>-169604000</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>-144919000</v>
+      </c>
+      <c r="G16" s="3" t="n"/>
+      <c r="H16" s="3" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Additional Paid In Capital</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>2913931000</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>1715787000</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>1401320000</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>864677000</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>412583000</v>
+      </c>
+      <c r="G17" s="3" t="n"/>
+      <c r="H17" s="3" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Capital Stock</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>17000</v>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>16000</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>16000</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>15000</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>14000</v>
+      </c>
+      <c r="G18" s="3" t="n"/>
+      <c r="H18" s="3" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Common Stock</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>17000</v>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>16000</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>16000</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>15000</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>14000</v>
+      </c>
+      <c r="G19" s="3" t="n"/>
+      <c r="H19" s="3" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Total Liabilities Net Minority Interest</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>64880000</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>52247000</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>40633000</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>34673000</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>32816000</v>
+      </c>
+      <c r="G20" s="3" t="n"/>
+      <c r="H20" s="3" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Total Non Current Liabilities Net Minority Interest</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>27744000</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>26701000</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>26830000</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>27059000</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>27161000</v>
+      </c>
+      <c r="G21" s="3" t="n"/>
+      <c r="H21" s="3" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Other Non Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>25000000</v>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>25000000</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>25000000</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>25000000</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>25000000</v>
+      </c>
+      <c r="G22" s="3" t="n"/>
+      <c r="H22" s="3" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Derivative Product Liabilities</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n"/>
+      <c r="C23" s="3" t="n"/>
+      <c r="D23" s="3" t="n"/>
+      <c r="E23" s="3" t="n"/>
+      <c r="F23" s="3" t="n"/>
+      <c r="G23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Liabilities</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>1155000</v>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>1155000</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>1049000</v>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>1049000</v>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>1049000</v>
+      </c>
+      <c r="G24" s="3" t="n"/>
+      <c r="H24" s="3" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Taxes Liabilities</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>1155000</v>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>1155000</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>1049000</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>1049000</v>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>1049000</v>
+      </c>
+      <c r="G25" s="3" t="n"/>
+      <c r="H25" s="3" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Long Term Debt And Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="n">
+        <v>1589000</v>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>546000</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>781000</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>1010000</v>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>1112000</v>
+      </c>
+      <c r="G26" s="3" t="n"/>
+      <c r="H26" s="3" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Long Term Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v>1589000</v>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>546000</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>781000</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>1010000</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>1112000</v>
+      </c>
+      <c r="G27" s="3" t="n"/>
+      <c r="H27" s="3" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="n">
+        <v>37136000</v>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>25546000</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>13803000</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>7614000</v>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>5655000</v>
+      </c>
+      <c r="G28" s="3" t="n"/>
+      <c r="H28" s="3" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Other Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="n">
+        <v>1556000</v>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>451000</v>
+      </c>
+      <c r="D29" s="3" t="n"/>
+      <c r="E29" s="3" t="n"/>
+      <c r="F29" s="3" t="n"/>
+      <c r="G29" s="3" t="n">
+        <v>463000</v>
+      </c>
+      <c r="H29" s="3" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Current Debt And Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="n">
+        <v>1031000</v>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>904000</v>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>1163000</v>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>1129000</v>
+      </c>
+      <c r="F30" s="3" t="n">
+        <v>941000</v>
+      </c>
+      <c r="G30" s="3" t="n"/>
+      <c r="H30" s="3" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Current Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v>1031000</v>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>904000</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>880000</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>854000</v>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>681000</v>
+      </c>
+      <c r="G31" s="3" t="n"/>
+      <c r="H31" s="3" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Current Debt</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="n"/>
+      <c r="C32" s="3" t="n"/>
+      <c r="D32" s="3" t="n">
+        <v>283000</v>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>275000</v>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v>260000</v>
+      </c>
+      <c r="G32" s="3" t="n">
+        <v>261000</v>
+      </c>
+      <c r="H32" s="3" t="n">
+        <v>226138</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Line Of Credit</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="n"/>
+      <c r="C33" s="3" t="n"/>
+      <c r="D33" s="3" t="n">
+        <v>283000</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>275000</v>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>260000</v>
+      </c>
+      <c r="G33" s="3" t="n">
+        <v>261000</v>
+      </c>
+      <c r="H33" s="3" t="n">
+        <v>226138</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Payables And Accrued Expenses</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="n">
+        <v>34549000</v>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>24191000</v>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>12640000</v>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>6485000</v>
+      </c>
+      <c r="F34" s="3" t="n">
+        <v>4714000</v>
+      </c>
+      <c r="G34" s="3" t="n"/>
+      <c r="H34" s="3" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Current Accrued Expenses</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="n">
+        <v>20340000</v>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v>20046000</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>10504000</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>3898000</v>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>2778000</v>
+      </c>
+      <c r="G35" s="3" t="n"/>
+      <c r="H35" s="3" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Payables</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="n">
+        <v>14209000</v>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>4145000</v>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>2136000</v>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>2587000</v>
+      </c>
+      <c r="F36" s="3" t="n">
+        <v>1936000</v>
+      </c>
+      <c r="G36" s="3" t="n"/>
+      <c r="H36" s="3" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total Tax Payable</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="n"/>
+      <c r="C37" s="3" t="n"/>
+      <c r="D37" s="3" t="n">
+        <v>113000</v>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>247000</v>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>506000</v>
+      </c>
+      <c r="G37" s="3" t="n">
+        <v>202000</v>
+      </c>
+      <c r="H37" s="3" t="n">
+        <v>2547731</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Income Tax Payable</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="n"/>
+      <c r="C38" s="3" t="n"/>
+      <c r="D38" s="3" t="n"/>
+      <c r="E38" s="3" t="n"/>
+      <c r="F38" s="3" t="n">
+        <v>506000</v>
+      </c>
+      <c r="G38" s="3" t="n"/>
+      <c r="H38" s="3" t="n">
+        <v>388584</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Accounts Payable</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="n">
+        <v>14209000</v>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v>4145000</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>2023000</v>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>2340000</v>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>1430000</v>
+      </c>
+      <c r="G39" s="3" t="n"/>
+      <c r="H39" s="3" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Total Assets</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="n">
+        <v>2703509000</v>
+      </c>
+      <c r="C40" s="3" t="n">
+        <v>1528457000</v>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>1246219000</v>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>731084000</v>
+      </c>
+      <c r="F40" s="3" t="n">
+        <v>302146000</v>
+      </c>
+      <c r="G40" s="3" t="n"/>
+      <c r="H40" s="3" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Total Non Current Assets</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="n">
+        <v>477851000</v>
+      </c>
+      <c r="C41" s="3" t="n">
+        <v>274688000</v>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>314440000</v>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>188422000</v>
+      </c>
+      <c r="F41" s="3" t="n">
+        <v>97240000</v>
+      </c>
+      <c r="G41" s="3" t="n"/>
+      <c r="H41" s="3" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Other Non Current Assets</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="n">
+        <v>17298000</v>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>217000</v>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>5182000</v>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>161000</v>
+      </c>
+      <c r="F42" s="3" t="n">
+        <v>157000</v>
+      </c>
+      <c r="G42" s="3" t="n"/>
+      <c r="H42" s="3" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Investments And Advances</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="n">
+        <v>328289000</v>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>196654000</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>261963000</v>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>148540000</v>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v>59670000</v>
+      </c>
+      <c r="G43" s="3" t="n"/>
+      <c r="H43" s="3" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Other Investments</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="n"/>
+      <c r="C44" s="3" t="n">
+        <v>12086000</v>
+      </c>
+      <c r="D44" s="3" t="n"/>
+      <c r="E44" s="3" t="n"/>
+      <c r="F44" s="3" t="n"/>
+      <c r="G44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" s="3" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Investmentin Financial Assets</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="n">
+        <v>328289000</v>
+      </c>
+      <c r="C45" s="3" t="n">
+        <v>184568000</v>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>261963000</v>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>148540000</v>
+      </c>
+      <c r="F45" s="3" t="n">
+        <v>59670000</v>
+      </c>
+      <c r="G45" s="3" t="n"/>
+      <c r="H45" s="3" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Held To Maturity Securities</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="n"/>
+      <c r="C46" s="3" t="n"/>
+      <c r="D46" s="3" t="n"/>
+      <c r="E46" s="3" t="n"/>
+      <c r="F46" s="3" t="n">
+        <v>59670000</v>
+      </c>
+      <c r="G46" s="3" t="n">
+        <v>47473000</v>
+      </c>
+      <c r="H46" s="3" t="n">
+        <v>57080461</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Available For Sale Securities</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="n">
+        <v>328289000</v>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>184568000</v>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v>261963000</v>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>148540000</v>
+      </c>
+      <c r="F47" s="3" t="n">
+        <v>59670000</v>
+      </c>
+      <c r="G47" s="3" t="n"/>
+      <c r="H47" s="3" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Goodwill And Other Intangible Assets</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="n">
+        <v>34121000</v>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>34121000</v>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>34220000</v>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>34220000</v>
+      </c>
+      <c r="F48" s="3" t="n">
+        <v>34220000</v>
+      </c>
+      <c r="G48" s="3" t="n"/>
+      <c r="H48" s="3" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Other Intangible Assets</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="n">
+        <v>27500000</v>
+      </c>
+      <c r="C49" s="3" t="n">
+        <v>27500000</v>
+      </c>
+      <c r="D49" s="3" t="n">
+        <v>27500000</v>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>27500000</v>
+      </c>
+      <c r="F49" s="3" t="n">
+        <v>27500000</v>
+      </c>
+      <c r="G49" s="3" t="n"/>
+      <c r="H49" s="3" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Goodwill</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="n">
+        <v>6621000</v>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>6621000</v>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>6720000</v>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>6720000</v>
+      </c>
+      <c r="F50" s="3" t="n">
+        <v>6720000</v>
+      </c>
+      <c r="G50" s="3" t="n"/>
+      <c r="H50" s="3" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Net PPE</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="n">
+        <v>98143000</v>
+      </c>
+      <c r="C51" s="3" t="n">
+        <v>43696000</v>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v>13075000</v>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>5501000</v>
+      </c>
+      <c r="F51" s="3" t="n">
+        <v>3193000</v>
+      </c>
+      <c r="G51" s="3" t="n"/>
+      <c r="H51" s="3" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Accumulated Depreciation</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="n">
+        <v>-1060000</v>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>-897000</v>
+      </c>
+      <c r="D52" s="3" t="n">
+        <v>-748000</v>
+      </c>
+      <c r="E52" s="3" t="n">
+        <v>-624000</v>
+      </c>
+      <c r="F52" s="3" t="n">
+        <v>-499000</v>
+      </c>
+      <c r="G52" s="3" t="n"/>
+      <c r="H52" s="3" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross PPE</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="n">
+        <v>99203000</v>
+      </c>
+      <c r="C53" s="3" t="n">
+        <v>44593000</v>
+      </c>
+      <c r="D53" s="3" t="n">
+        <v>13823000</v>
+      </c>
+      <c r="E53" s="3" t="n">
+        <v>6125000</v>
+      </c>
+      <c r="F53" s="3" t="n">
+        <v>3692000</v>
+      </c>
+      <c r="G53" s="3" t="n"/>
+      <c r="H53" s="3" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Leases</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="n">
+        <v>62000</v>
+      </c>
+      <c r="C54" s="3" t="n">
+        <v>62000</v>
+      </c>
+      <c r="D54" s="3" t="n">
+        <v>62000</v>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v>62000</v>
+      </c>
+      <c r="F54" s="3" t="n">
+        <v>93000</v>
+      </c>
+      <c r="G54" s="3" t="n"/>
+      <c r="H54" s="3" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Construction In Progress</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="n">
+        <v>89032000</v>
+      </c>
+      <c r="C55" s="3" t="n">
+        <v>35748000</v>
+      </c>
+      <c r="D55" s="3" t="n">
+        <v>10530000</v>
+      </c>
+      <c r="E55" s="3" t="n">
+        <v>2645000</v>
+      </c>
+      <c r="F55" s="3" t="n"/>
+      <c r="G55" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" s="3" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Other Properties</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="n">
+        <v>10109000</v>
+      </c>
+      <c r="C56" s="3" t="n">
+        <v>8783000</v>
+      </c>
+      <c r="D56" s="3" t="n">
+        <v>3231000</v>
+      </c>
+      <c r="E56" s="3" t="n">
+        <v>3418000</v>
+      </c>
+      <c r="F56" s="3" t="n">
+        <v>3599000</v>
+      </c>
+      <c r="G56" s="3" t="n"/>
+      <c r="H56" s="3" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Current Assets</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="n">
+        <v>2225658000</v>
+      </c>
+      <c r="C57" s="3" t="n">
+        <v>1253769000</v>
+      </c>
+      <c r="D57" s="3" t="n">
+        <v>931779000</v>
+      </c>
+      <c r="E57" s="3" t="n">
+        <v>542662000</v>
+      </c>
+      <c r="F57" s="3" t="n">
+        <v>204906000</v>
+      </c>
+      <c r="G57" s="3" t="n"/>
+      <c r="H57" s="3" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Other Current Assets</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="n">
+        <v>1669000</v>
+      </c>
+      <c r="C58" s="3" t="n">
+        <v>1969000</v>
+      </c>
+      <c r="D58" s="3" t="n">
+        <v>46000</v>
+      </c>
+      <c r="E58" s="3" t="n">
+        <v>38000</v>
+      </c>
+      <c r="F58" s="3" t="n">
+        <v>160000</v>
+      </c>
+      <c r="G58" s="3" t="n"/>
+      <c r="H58" s="3" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Current Deferred Assets</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="n"/>
+      <c r="C59" s="3" t="n"/>
+      <c r="D59" s="3" t="n"/>
+      <c r="E59" s="3" t="n"/>
+      <c r="F59" s="3" t="n"/>
+      <c r="G59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H59" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Prepaid Assets</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="n">
+        <v>5670000</v>
+      </c>
+      <c r="C60" s="3" t="n">
+        <v>18853000</v>
+      </c>
+      <c r="D60" s="3" t="n">
+        <v>4898000</v>
+      </c>
+      <c r="E60" s="3" t="n">
+        <v>5373000</v>
+      </c>
+      <c r="F60" s="3" t="n">
+        <v>2085000</v>
+      </c>
+      <c r="G60" s="3" t="n"/>
+      <c r="H60" s="3" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Receivables</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="n">
+        <v>9710000</v>
+      </c>
+      <c r="C61" s="3" t="n">
+        <v>4976000</v>
+      </c>
+      <c r="D61" s="3" t="n">
+        <v>5235000</v>
+      </c>
+      <c r="E61" s="3" t="n">
+        <v>2826000</v>
+      </c>
+      <c r="F61" s="3" t="n">
+        <v>1643000</v>
+      </c>
+      <c r="G61" s="3" t="n"/>
+      <c r="H61" s="3" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Other Receivables</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="n"/>
+      <c r="C62" s="3" t="n"/>
+      <c r="D62" s="3" t="n">
+        <v>518000</v>
+      </c>
+      <c r="E62" s="3" t="n">
+        <v>189000</v>
+      </c>
+      <c r="F62" s="3" t="n">
+        <v>307000</v>
+      </c>
+      <c r="G62" s="3" t="n">
+        <v>600000</v>
+      </c>
+      <c r="H62" s="3" t="n">
+        <v>433985</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Accrued Interest Receivable</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="n">
+        <v>9710000</v>
+      </c>
+      <c r="C63" s="3" t="n">
+        <v>4976000</v>
+      </c>
+      <c r="D63" s="3" t="n">
+        <v>4717000</v>
+      </c>
+      <c r="E63" s="3" t="n">
+        <v>2637000</v>
+      </c>
+      <c r="F63" s="3" t="n">
+        <v>1336000</v>
+      </c>
+      <c r="G63" s="3" t="n"/>
+      <c r="H63" s="3" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Cash Cash Equivalents And Short Term Investments</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="n">
+        <v>2208609000</v>
+      </c>
+      <c r="C64" s="3" t="n">
+        <v>1227971000</v>
+      </c>
+      <c r="D64" s="3" t="n">
+        <v>921600000</v>
+      </c>
+      <c r="E64" s="3" t="n">
+        <v>534425000</v>
+      </c>
+      <c r="F64" s="3" t="n">
+        <v>201018000</v>
+      </c>
+      <c r="G64" s="3" t="n"/>
+      <c r="H64" s="3" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Other Short Term Investments</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="n">
+        <v>614506000</v>
+      </c>
+      <c r="C65" s="3" t="n">
+        <v>439526000</v>
+      </c>
+      <c r="D65" s="3" t="n">
+        <v>511559000</v>
+      </c>
+      <c r="E65" s="3" t="n">
+        <v>307654000</v>
+      </c>
+      <c r="F65" s="3" t="n">
+        <v>110940000</v>
+      </c>
+      <c r="G65" s="3" t="n"/>
+      <c r="H65" s="3" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Cash And Cash Equivalents</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="n">
+        <v>1594103000</v>
+      </c>
+      <c r="C66" s="3" t="n">
+        <v>788445000</v>
+      </c>
+      <c r="D66" s="3" t="n">
+        <v>410041000</v>
+      </c>
+      <c r="E66" s="3" t="n">
+        <v>226771000</v>
+      </c>
+      <c r="F66" s="3" t="n">
+        <v>90078000</v>
+      </c>
+      <c r="G66" s="3" t="n"/>
+      <c r="H66" s="3" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Cash Equivalents</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="n"/>
+      <c r="C67" s="3" t="n">
+        <v>777423000</v>
+      </c>
+      <c r="D67" s="3" t="n">
+        <v>402241000</v>
+      </c>
+      <c r="E67" s="3" t="n"/>
+      <c r="F67" s="3" t="n"/>
+      <c r="G67" s="3" t="n">
+        <v>94112000</v>
+      </c>
+      <c r="H67" s="3" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Cash Financial</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="n"/>
+      <c r="C68" s="3" t="n">
+        <v>11022000</v>
+      </c>
+      <c r="D68" s="3" t="n">
+        <v>7800000</v>
+      </c>
+      <c r="E68" s="3" t="n"/>
+      <c r="F68" s="3" t="n"/>
+      <c r="G68" s="3" t="n">
+        <v>3020000</v>
+      </c>
+      <c r="H68" s="3" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4701,13 +6844,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G45"/>
+  <dimension ref="A1:H45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4717,6 +6860,7 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4727,30 +6871,35 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>2025-12-31</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>2025-06-30</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>2025-03-31</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>2024-12-31</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>2024-09-30</t>
         </is>
@@ -4763,21 +6912,22 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>-50677000</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>-60379000</v>
       </c>
-      <c r="C2" s="3" t="n">
+      <c r="D2" s="3" t="n">
         <v>-23077000</v>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="E2" s="3" t="n">
         <v>-19348000</v>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="F2" s="3" t="n">
         <v>-12575000</v>
       </c>
-      <c r="F2" s="3" t="n">
-        <v>-13538743</v>
-      </c>
       <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -4786,17 +6936,22 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
+        <v>1181897000</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>295500000</v>
       </c>
-      <c r="C3" s="3" t="n">
+      <c r="D3" s="3" t="n">
         <v>526499000</v>
       </c>
-      <c r="D3" s="3" t="n"/>
-      <c r="E3" s="3" t="n"/>
-      <c r="F3" s="3" t="n"/>
-      <c r="G3" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="E3" s="3" t="n">
+        <v>441600000</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -4805,21 +6960,22 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
+        <v>-32810000</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>-26950000</v>
       </c>
-      <c r="C4" s="3" t="n">
+      <c r="D4" s="3" t="n">
         <v>-5046000</v>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="E4" s="3" t="n">
         <v>-877000</v>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="F4" s="3" t="n">
         <v>-332000</v>
       </c>
-      <c r="F4" s="3" t="n">
-        <v>-69381</v>
-      </c>
       <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -4831,10 +6987,11 @@
       <c r="C5" s="3" t="n"/>
       <c r="D5" s="3" t="n"/>
       <c r="E5" s="3" t="n"/>
-      <c r="F5" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="F5" s="3" t="n"/>
       <c r="G5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4845,15 +7002,16 @@
         </is>
       </c>
       <c r="B6" s="3" t="n"/>
-      <c r="C6" s="3" t="n">
+      <c r="C6" s="3" t="n"/>
+      <c r="D6" s="3" t="n">
         <v>684000</v>
       </c>
-      <c r="D6" s="3" t="n"/>
       <c r="E6" s="3" t="n"/>
-      <c r="F6" s="3" t="n">
+      <c r="F6" s="3" t="n"/>
+      <c r="G6" s="3" t="n">
         <v>550110</v>
       </c>
-      <c r="G6" s="3" t="n">
+      <c r="H6" s="3" t="n">
         <v>357000</v>
       </c>
     </row>
@@ -4864,21 +7022,22 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
+        <v>1594103000</v>
+      </c>
+      <c r="C7" s="3" t="n">
         <v>788445000</v>
       </c>
-      <c r="C7" s="3" t="n">
+      <c r="D7" s="3" t="n">
         <v>410041000</v>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="E7" s="3" t="n">
         <v>226771000</v>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="F7" s="3" t="n">
         <v>90078000</v>
       </c>
-      <c r="F7" s="3" t="n">
-        <v>97132000</v>
-      </c>
       <c r="G7" s="3" t="n"/>
+      <c r="H7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -4887,21 +7046,22 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
+        <v>788445000</v>
+      </c>
+      <c r="C8" s="3" t="n">
         <v>410041000</v>
       </c>
-      <c r="C8" s="3" t="n">
+      <c r="D8" s="3" t="n">
         <v>226771000</v>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="E8" s="3" t="n">
         <v>90078000</v>
       </c>
-      <c r="E8" s="3" t="n">
+      <c r="F8" s="3" t="n">
         <v>97132000</v>
       </c>
-      <c r="F8" s="3" t="n">
-        <v>91799754</v>
-      </c>
       <c r="G8" s="3" t="n"/>
+      <c r="H8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -4910,21 +7070,22 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
+        <v>805658000</v>
+      </c>
+      <c r="C9" s="3" t="n">
         <v>378404000</v>
       </c>
-      <c r="C9" s="3" t="n">
+      <c r="D9" s="3" t="n">
         <v>183270000</v>
       </c>
-      <c r="D9" s="3" t="n">
+      <c r="E9" s="3" t="n">
         <v>136693000</v>
       </c>
-      <c r="E9" s="3" t="n">
+      <c r="F9" s="3" t="n">
         <v>-7054000</v>
       </c>
-      <c r="F9" s="3" t="n">
-        <v>5331834</v>
-      </c>
       <c r="G9" s="3" t="n"/>
+      <c r="H9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -4933,21 +7094,22 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
+        <v>1182559000</v>
+      </c>
+      <c r="C10" s="3" t="n">
         <v>295606000</v>
       </c>
-      <c r="C10" s="3" t="n">
+      <c r="D10" s="3" t="n">
         <v>526511000</v>
       </c>
-      <c r="D10" s="3" t="n">
+      <c r="E10" s="3" t="n">
         <v>441924000</v>
       </c>
-      <c r="E10" s="3" t="n">
+      <c r="F10" s="3" t="n">
         <v>-875000</v>
       </c>
-      <c r="F10" s="3" t="n">
-        <v>603959</v>
-      </c>
       <c r="G10" s="3" t="n"/>
+      <c r="H10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -4956,21 +7118,22 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
+        <v>1182559000</v>
+      </c>
+      <c r="C11" s="3" t="n">
         <v>295606000</v>
       </c>
-      <c r="C11" s="3" t="n">
+      <c r="D11" s="3" t="n">
         <v>526511000</v>
       </c>
-      <c r="D11" s="3" t="n">
+      <c r="E11" s="3" t="n">
         <v>441924000</v>
       </c>
-      <c r="E11" s="3" t="n">
+      <c r="F11" s="3" t="n">
         <v>-875000</v>
       </c>
-      <c r="F11" s="3" t="n">
-        <v>603959</v>
-      </c>
       <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -4979,21 +7142,22 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
+        <v>-75000</v>
+      </c>
+      <c r="C12" s="3" t="n">
         <v>-1177000</v>
       </c>
-      <c r="C12" s="3" t="n">
+      <c r="D12" s="3" t="n">
         <v>-1385000</v>
       </c>
-      <c r="D12" s="3" t="n">
+      <c r="E12" s="3" t="n">
         <v>-304000</v>
       </c>
-      <c r="E12" s="3" t="n">
+      <c r="F12" s="3" t="n">
         <v>-1595000</v>
       </c>
-      <c r="F12" s="3" t="n">
-        <v>-119</v>
-      </c>
       <c r="G12" s="3" t="n"/>
+      <c r="H12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -5002,21 +7166,22 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
+        <v>737000</v>
+      </c>
+      <c r="C13" s="3" t="n">
         <v>1283000</v>
       </c>
-      <c r="C13" s="3" t="n">
+      <c r="D13" s="3" t="n">
         <v>1397000</v>
       </c>
-      <c r="D13" s="3" t="n">
+      <c r="E13" s="3" t="n">
         <v>628000</v>
       </c>
-      <c r="E13" s="3" t="n">
+      <c r="F13" s="3" t="n">
         <v>720000</v>
       </c>
-      <c r="F13" s="3" t="n">
-        <v>604078</v>
-      </c>
       <c r="G13" s="3" t="n"/>
+      <c r="H13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -5025,17 +7190,22 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
+        <v>1181897000</v>
+      </c>
+      <c r="C14" s="3" t="n">
         <v>295500000</v>
       </c>
-      <c r="C14" s="3" t="n">
+      <c r="D14" s="3" t="n">
         <v>526499000</v>
       </c>
-      <c r="D14" s="3" t="n"/>
-      <c r="E14" s="3" t="n"/>
-      <c r="F14" s="3" t="n"/>
-      <c r="G14" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="E14" s="3" t="n">
+        <v>441600000</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3" t="n"/>
+      <c r="H14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -5044,17 +7214,22 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
+        <v>1181897000</v>
+      </c>
+      <c r="C15" s="3" t="n">
         <v>295500000</v>
       </c>
-      <c r="C15" s="3" t="n">
+      <c r="D15" s="3" t="n">
         <v>526499000</v>
       </c>
-      <c r="D15" s="3" t="n"/>
-      <c r="E15" s="3" t="n"/>
-      <c r="F15" s="3" t="n"/>
-      <c r="G15" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="E15" s="3" t="n">
+        <v>441600000</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="3" t="n"/>
+      <c r="H15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -5063,21 +7238,22 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
+        <v>-359034000</v>
+      </c>
+      <c r="C16" s="3" t="n">
         <v>116227000</v>
       </c>
-      <c r="C16" s="3" t="n">
+      <c r="D16" s="3" t="n">
         <v>-325210000</v>
       </c>
-      <c r="D16" s="3" t="n">
+      <c r="E16" s="3" t="n">
         <v>-286760000</v>
       </c>
-      <c r="E16" s="3" t="n">
+      <c r="F16" s="3" t="n">
         <v>6064000</v>
       </c>
-      <c r="F16" s="3" t="n">
-        <v>18197237</v>
-      </c>
       <c r="G16" s="3" t="n"/>
+      <c r="H16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -5086,21 +7262,22 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
+        <v>-359034000</v>
+      </c>
+      <c r="C17" s="3" t="n">
         <v>116227000</v>
       </c>
-      <c r="C17" s="3" t="n">
+      <c r="D17" s="3" t="n">
         <v>-325210000</v>
       </c>
-      <c r="D17" s="3" t="n">
+      <c r="E17" s="3" t="n">
         <v>-286760000</v>
       </c>
-      <c r="E17" s="3" t="n">
+      <c r="F17" s="3" t="n">
         <v>6064000</v>
       </c>
-      <c r="F17" s="3" t="n">
-        <v>18197237</v>
-      </c>
       <c r="G17" s="3" t="n"/>
+      <c r="H17" s="3" t="n"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -5109,21 +7286,22 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
+        <v>-326224000</v>
+      </c>
+      <c r="C18" s="3" t="n">
         <v>143177000</v>
       </c>
-      <c r="C18" s="3" t="n">
+      <c r="D18" s="3" t="n">
         <v>-320164000</v>
       </c>
-      <c r="D18" s="3" t="n">
+      <c r="E18" s="3" t="n">
         <v>-285883000</v>
       </c>
-      <c r="E18" s="3" t="n">
+      <c r="F18" s="3" t="n">
         <v>7296000</v>
       </c>
-      <c r="F18" s="3" t="n">
-        <v>18266618</v>
-      </c>
       <c r="G18" s="3" t="n"/>
+      <c r="H18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -5132,21 +7310,22 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
+        <v>130454000</v>
+      </c>
+      <c r="C19" s="3" t="n">
         <v>214148000</v>
       </c>
-      <c r="C19" s="3" t="n">
+      <c r="D19" s="3" t="n">
         <v>94827000</v>
       </c>
-      <c r="D19" s="3" t="n">
+      <c r="E19" s="3" t="n">
         <v>30834000</v>
       </c>
-      <c r="E19" s="3" t="n">
+      <c r="F19" s="3" t="n">
         <v>37183000</v>
       </c>
-      <c r="F19" s="3" t="n">
-        <v>48804940</v>
-      </c>
       <c r="G19" s="3" t="n"/>
+      <c r="H19" s="3" t="n"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -5155,21 +7334,22 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
+        <v>-456678000</v>
+      </c>
+      <c r="C20" s="3" t="n">
         <v>-70971000</v>
       </c>
-      <c r="C20" s="3" t="n">
+      <c r="D20" s="3" t="n">
         <v>-414991000</v>
       </c>
-      <c r="D20" s="3" t="n">
+      <c r="E20" s="3" t="n">
         <v>-316717000</v>
       </c>
-      <c r="E20" s="3" t="n">
+      <c r="F20" s="3" t="n">
         <v>-29887000</v>
       </c>
-      <c r="F20" s="3" t="n">
-        <v>-30538322</v>
-      </c>
       <c r="G20" s="3" t="n"/>
+      <c r="H20" s="3" t="n"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -5187,12 +7367,13 @@
         <v>0</v>
       </c>
       <c r="E21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="3" t="n">
         <v>-900000</v>
       </c>
-      <c r="F21" s="3" t="n"/>
-      <c r="G21" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="G21" s="3" t="n"/>
+      <c r="H21" s="3" t="n"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -5210,12 +7391,13 @@
         <v>0</v>
       </c>
       <c r="E22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="3" t="n">
         <v>-900000</v>
       </c>
-      <c r="F22" s="3" t="n"/>
-      <c r="G22" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="G22" s="3" t="n"/>
+      <c r="H22" s="3" t="n"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -5224,21 +7406,22 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
+        <v>-32810000</v>
+      </c>
+      <c r="C23" s="3" t="n">
         <v>-26950000</v>
       </c>
-      <c r="C23" s="3" t="n">
+      <c r="D23" s="3" t="n">
         <v>-5046000</v>
       </c>
-      <c r="D23" s="3" t="n">
+      <c r="E23" s="3" t="n">
         <v>-877000</v>
       </c>
-      <c r="E23" s="3" t="n">
+      <c r="F23" s="3" t="n">
         <v>-332000</v>
       </c>
-      <c r="F23" s="3" t="n">
-        <v>-69381</v>
-      </c>
       <c r="G23" s="3" t="n"/>
+      <c r="H23" s="3" t="n"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -5247,21 +7430,22 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
+        <v>-32810000</v>
+      </c>
+      <c r="C24" s="3" t="n">
         <v>-26950000</v>
       </c>
-      <c r="C24" s="3" t="n">
+      <c r="D24" s="3" t="n">
         <v>-5046000</v>
       </c>
-      <c r="D24" s="3" t="n">
+      <c r="E24" s="3" t="n">
         <v>-877000</v>
       </c>
-      <c r="E24" s="3" t="n">
+      <c r="F24" s="3" t="n">
         <v>-332000</v>
       </c>
-      <c r="F24" s="3" t="n">
-        <v>-69381</v>
-      </c>
       <c r="G24" s="3" t="n"/>
+      <c r="H24" s="3" t="n"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -5270,21 +7454,22 @@
         </is>
       </c>
       <c r="B25" s="3" t="n">
+        <v>-17867000</v>
+      </c>
+      <c r="C25" s="3" t="n">
         <v>-33429000</v>
       </c>
-      <c r="C25" s="3" t="n">
+      <c r="D25" s="3" t="n">
         <v>-18031000</v>
       </c>
-      <c r="D25" s="3" t="n">
+      <c r="E25" s="3" t="n">
         <v>-18471000</v>
       </c>
-      <c r="E25" s="3" t="n">
+      <c r="F25" s="3" t="n">
         <v>-12243000</v>
       </c>
-      <c r="F25" s="3" t="n">
-        <v>-13469362</v>
-      </c>
       <c r="G25" s="3" t="n"/>
+      <c r="H25" s="3" t="n"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -5293,21 +7478,22 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
+        <v>-17867000</v>
+      </c>
+      <c r="C26" s="3" t="n">
         <v>-33429000</v>
       </c>
-      <c r="C26" s="3" t="n">
+      <c r="D26" s="3" t="n">
         <v>-18031000</v>
       </c>
-      <c r="D26" s="3" t="n">
+      <c r="E26" s="3" t="n">
         <v>-18471000</v>
       </c>
-      <c r="E26" s="3" t="n">
+      <c r="F26" s="3" t="n">
         <v>-12243000</v>
       </c>
-      <c r="F26" s="3" t="n">
-        <v>-13469362</v>
-      </c>
       <c r="G26" s="3" t="n"/>
+      <c r="H26" s="3" t="n"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -5316,21 +7502,22 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
+        <v>-413000</v>
+      </c>
+      <c r="C27" s="3" t="n">
         <v>-8104000</v>
       </c>
-      <c r="C27" s="3" t="n">
+      <c r="D27" s="3" t="n">
         <v>2358000</v>
       </c>
-      <c r="D27" s="3" t="n">
+      <c r="E27" s="3" t="n">
         <v>-5246000</v>
       </c>
-      <c r="E27" s="3" t="n">
+      <c r="F27" s="3" t="n">
         <v>178000</v>
       </c>
-      <c r="F27" s="3" t="n">
-        <v>-2686581</v>
-      </c>
       <c r="G27" s="3" t="n"/>
+      <c r="H27" s="3" t="n"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -5339,21 +7526,22 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
+        <v>26000</v>
+      </c>
+      <c r="C28" s="3" t="n">
         <v>-6000</v>
       </c>
-      <c r="C28" s="3" t="n">
+      <c r="D28" s="3" t="n">
         <v>-2000</v>
       </c>
-      <c r="D28" s="3" t="n">
+      <c r="E28" s="3" t="n">
         <v>24000</v>
       </c>
-      <c r="E28" s="3" t="n">
+      <c r="F28" s="3" t="n">
         <v>8000</v>
       </c>
-      <c r="F28" s="3" t="n"/>
-      <c r="G28" s="3" t="n">
-        <v>44000</v>
-      </c>
+      <c r="G28" s="3" t="n"/>
+      <c r="H28" s="3" t="n"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -5365,10 +7553,11 @@
       <c r="C29" s="3" t="n"/>
       <c r="D29" s="3" t="n"/>
       <c r="E29" s="3" t="n"/>
-      <c r="F29" s="3" t="n">
+      <c r="F29" s="3" t="n"/>
+      <c r="G29" s="3" t="n">
         <v>-2409</v>
       </c>
-      <c r="G29" s="3" t="n">
+      <c r="H29" s="3" t="n">
         <v>44667</v>
       </c>
     </row>
@@ -5379,21 +7568,22 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
+        <v>5000</v>
+      </c>
+      <c r="C30" s="3" t="n">
         <v>-35000</v>
       </c>
-      <c r="C30" s="3" t="n">
+      <c r="D30" s="3" t="n">
         <v>-21000</v>
       </c>
-      <c r="D30" s="3" t="n">
+      <c r="E30" s="3" t="n">
         <v>-4000</v>
       </c>
-      <c r="E30" s="3" t="n">
+      <c r="F30" s="3" t="n">
         <v>-17000</v>
       </c>
-      <c r="F30" s="3" t="n">
-        <v>-25361</v>
-      </c>
       <c r="G30" s="3" t="n"/>
+      <c r="H30" s="3" t="n"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -5402,21 +7592,22 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
+        <v>-9193000</v>
+      </c>
+      <c r="C31" s="3" t="n">
         <v>7556000</v>
       </c>
-      <c r="C31" s="3" t="n">
+      <c r="D31" s="3" t="n">
         <v>4323000</v>
       </c>
-      <c r="D31" s="3" t="n">
+      <c r="E31" s="3" t="n">
         <v>-917000</v>
       </c>
-      <c r="E31" s="3" t="n">
+      <c r="F31" s="3" t="n">
         <v>-149000</v>
       </c>
-      <c r="F31" s="3" t="n">
-        <v>-1972013</v>
-      </c>
       <c r="G31" s="3" t="n"/>
+      <c r="H31" s="3" t="n"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -5425,21 +7616,22 @@
         </is>
       </c>
       <c r="B32" s="3" t="n">
+        <v>-9132000</v>
+      </c>
+      <c r="C32" s="3" t="n">
         <v>7894000</v>
       </c>
-      <c r="C32" s="3" t="n">
+      <c r="D32" s="3" t="n">
         <v>3061000</v>
       </c>
-      <c r="D32" s="3" t="n">
+      <c r="E32" s="3" t="n">
         <v>-216000</v>
       </c>
-      <c r="E32" s="3" t="n">
+      <c r="F32" s="3" t="n">
         <v>1606000</v>
       </c>
-      <c r="F32" s="3" t="n">
-        <v>-2134339</v>
-      </c>
       <c r="G32" s="3" t="n"/>
+      <c r="H32" s="3" t="n"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -5448,21 +7640,22 @@
         </is>
       </c>
       <c r="B33" s="3" t="n">
+        <v>-61000</v>
+      </c>
+      <c r="C33" s="3" t="n">
         <v>-338000</v>
       </c>
-      <c r="C33" s="3" t="n">
+      <c r="D33" s="3" t="n">
         <v>1262000</v>
       </c>
-      <c r="D33" s="3" t="n">
+      <c r="E33" s="3" t="n">
         <v>-701000</v>
       </c>
-      <c r="E33" s="3" t="n">
+      <c r="F33" s="3" t="n">
         <v>-1755000</v>
       </c>
-      <c r="F33" s="3" t="n">
-        <v>162326</v>
-      </c>
       <c r="G33" s="3" t="n"/>
+      <c r="H33" s="3" t="n"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -5471,21 +7664,22 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
+        <v>-61000</v>
+      </c>
+      <c r="C34" s="3" t="n">
         <v>-338000</v>
       </c>
-      <c r="C34" s="3" t="n">
+      <c r="D34" s="3" t="n">
         <v>1262000</v>
       </c>
-      <c r="D34" s="3" t="n">
+      <c r="E34" s="3" t="n">
         <v>-701000</v>
       </c>
-      <c r="E34" s="3" t="n">
+      <c r="F34" s="3" t="n">
         <v>-1755000</v>
       </c>
-      <c r="F34" s="3" t="n">
-        <v>162326</v>
-      </c>
       <c r="G34" s="3" t="n"/>
+      <c r="H34" s="3" t="n"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -5494,21 +7688,22 @@
         </is>
       </c>
       <c r="B35" s="3" t="n">
+        <v>8749000</v>
+      </c>
+      <c r="C35" s="3" t="n">
         <v>-15619000</v>
       </c>
-      <c r="C35" s="3" t="n">
+      <c r="D35" s="3" t="n">
         <v>-1942000</v>
       </c>
-      <c r="D35" s="3" t="n">
+      <c r="E35" s="3" t="n">
         <v>-4349000</v>
       </c>
-      <c r="E35" s="3" t="n">
+      <c r="F35" s="3" t="n">
         <v>336000</v>
       </c>
-      <c r="F35" s="3" t="n">
-        <v>-686798</v>
-      </c>
       <c r="G35" s="3" t="n"/>
+      <c r="H35" s="3" t="n"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -5517,21 +7712,22 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
+        <v>15586000</v>
+      </c>
+      <c r="C36" s="3" t="n">
         <v>18999000</v>
       </c>
-      <c r="C36" s="3" t="n">
+      <c r="D36" s="3" t="n">
         <v>9120000</v>
       </c>
-      <c r="D36" s="3" t="n">
+      <c r="E36" s="3" t="n">
         <v>11365000</v>
       </c>
-      <c r="E36" s="3" t="n">
+      <c r="F36" s="3" t="n">
         <v>2311000</v>
       </c>
-      <c r="F36" s="3" t="n">
-        <v>1733220</v>
-      </c>
       <c r="G36" s="3" t="n"/>
+      <c r="H36" s="3" t="n"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -5540,21 +7736,22 @@
         </is>
       </c>
       <c r="B37" s="3" t="n">
+        <v>-138000</v>
+      </c>
+      <c r="C37" s="3" t="n">
         <v>-3232000</v>
       </c>
-      <c r="C37" s="3" t="n">
+      <c r="D37" s="3" t="n">
         <v>89000</v>
       </c>
-      <c r="D37" s="3" t="n">
+      <c r="E37" s="3" t="n">
         <v>-30000</v>
       </c>
-      <c r="E37" s="3" t="n">
+      <c r="F37" s="3" t="n">
         <v>-312000</v>
       </c>
-      <c r="F37" s="3" t="n">
-        <v>-258855</v>
-      </c>
       <c r="G37" s="3" t="n"/>
+      <c r="H37" s="3" t="n"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -5563,21 +7760,22 @@
         </is>
       </c>
       <c r="B38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C38" s="3" t="n">
         <v>205000</v>
       </c>
-      <c r="C38" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="D38" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" s="3" t="n">
         <v>-4734000</v>
       </c>
-      <c r="F38" s="3" t="n"/>
-      <c r="G38" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="G38" s="3" t="n"/>
+      <c r="H38" s="3" t="n"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -5586,21 +7784,22 @@
         </is>
       </c>
       <c r="B39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" s="3" t="n">
         <v>205000</v>
       </c>
-      <c r="C39" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="D39" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" s="3" t="n">
         <v>-4734000</v>
       </c>
-      <c r="F39" s="3" t="n"/>
-      <c r="G39" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="G39" s="3" t="n"/>
+      <c r="H39" s="3" t="n"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -5609,21 +7808,22 @@
         </is>
       </c>
       <c r="B40" s="3" t="n">
+        <v>163000</v>
+      </c>
+      <c r="C40" s="3" t="n">
         <v>149000</v>
       </c>
-      <c r="C40" s="3" t="n">
+      <c r="D40" s="3" t="n">
         <v>124000</v>
       </c>
-      <c r="D40" s="3" t="n">
+      <c r="E40" s="3" t="n">
         <v>125000</v>
       </c>
-      <c r="E40" s="3" t="n">
+      <c r="F40" s="3" t="n">
         <v>124000</v>
       </c>
-      <c r="F40" s="3" t="n">
-        <v>87580</v>
-      </c>
       <c r="G40" s="3" t="n"/>
+      <c r="H40" s="3" t="n"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -5632,21 +7832,22 @@
         </is>
       </c>
       <c r="B41" s="3" t="n">
+        <v>163000</v>
+      </c>
+      <c r="C41" s="3" t="n">
         <v>149000</v>
       </c>
-      <c r="C41" s="3" t="n">
+      <c r="D41" s="3" t="n">
         <v>124000</v>
       </c>
-      <c r="D41" s="3" t="n">
+      <c r="E41" s="3" t="n">
         <v>125000</v>
       </c>
-      <c r="E41" s="3" t="n">
+      <c r="F41" s="3" t="n">
         <v>124000</v>
       </c>
-      <c r="F41" s="3" t="n">
-        <v>87580</v>
-      </c>
       <c r="G41" s="3" t="n"/>
+      <c r="H41" s="3" t="n"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -5654,14 +7855,17 @@
           <t>Depreciation</t>
         </is>
       </c>
-      <c r="B42" s="3" t="n"/>
+      <c r="B42" s="3" t="n">
+        <v>163000</v>
+      </c>
       <c r="C42" s="3" t="n"/>
       <c r="D42" s="3" t="n"/>
-      <c r="E42" s="3" t="n">
+      <c r="E42" s="3" t="n"/>
+      <c r="F42" s="3" t="n">
         <v>124000</v>
       </c>
-      <c r="F42" s="3" t="n"/>
       <c r="G42" s="3" t="n"/>
+      <c r="H42" s="3" t="n"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -5673,10 +7877,11 @@
       <c r="C43" s="3" t="n"/>
       <c r="D43" s="3" t="n"/>
       <c r="E43" s="3" t="n"/>
-      <c r="F43" s="3" t="n">
+      <c r="F43" s="3" t="n"/>
+      <c r="G43" s="3" t="n">
         <v>-2055959</v>
       </c>
-      <c r="G43" s="3" t="n">
+      <c r="H43" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5690,10 +7895,11 @@
       <c r="C44" s="3" t="n"/>
       <c r="D44" s="3" t="n"/>
       <c r="E44" s="3" t="n"/>
-      <c r="F44" s="3" t="n">
+      <c r="F44" s="3" t="n"/>
+      <c r="G44" s="3" t="n">
         <v>-2055959</v>
       </c>
-      <c r="G44" s="3" t="n">
+      <c r="H44" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5704,34 +7910,35 @@
         </is>
       </c>
       <c r="B45" s="3" t="n">
+        <v>-33065000</v>
+      </c>
+      <c r="C45" s="3" t="n">
         <v>-41446000</v>
       </c>
-      <c r="C45" s="3" t="n">
+      <c r="D45" s="3" t="n">
         <v>-29722000</v>
       </c>
-      <c r="D45" s="3" t="n">
+      <c r="E45" s="3" t="n">
         <v>-24685000</v>
       </c>
-      <c r="E45" s="3" t="n">
+      <c r="F45" s="3" t="n">
         <v>-9810000</v>
       </c>
-      <c r="F45" s="3" t="n">
-        <v>-10288767</v>
-      </c>
       <c r="G45" s="3" t="n"/>
+      <c r="H45" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -5786,6 +7993,30 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>FY Summary</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>'Gross Profit' not found in statements — left blank</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>FY Summary</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>'Net Debt' not found in statements — left blank</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
